--- a/static/documents/Team-Member-Nomination.xlsx
+++ b/static/documents/Team-Member-Nomination.xlsx
@@ -8,14 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/29a63266d5573dc2/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="94" documentId="8_{BDE1C76A-3272-4280-B0AF-4DC815AA2637}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C2B523E-4292-4161-B277-E536438107A3}"/>
+  <xr:revisionPtr revIDLastSave="138" documentId="8_{BDE1C76A-3272-4280-B0AF-4DC815AA2637}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D0AA614-7605-40B9-9CB3-9AD88CA7280C}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{95E92C69-2C53-4A25-9B67-D898DBE68FD6}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
-    <sheet name="Tabelle2" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet name="Tabelle2" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Tabelle1!$A$1:$H$51</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -40,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="31">
   <si>
     <t>Team</t>
   </si>
@@ -75,9 +78,6 @@
     <t>Participant Teams Official Meeting</t>
   </si>
   <si>
-    <t>Special Requests</t>
-  </si>
-  <si>
     <t>Number of cars  / parking permits</t>
   </si>
   <si>
@@ -127,6 +127,15 @@
   </si>
   <si>
     <t>Passport / ID Number</t>
+  </si>
+  <si>
+    <t>Startgroup</t>
+  </si>
+  <si>
+    <t>Special Request</t>
+  </si>
+  <si>
+    <t>SIAC Number</t>
   </si>
 </sst>
 </file>
@@ -209,26 +218,6 @@
         <color indexed="64"/>
       </left>
       <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -250,11 +239,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -304,26 +313,23 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -345,10 +351,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -668,34 +670,38 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88EA4317-FB20-408E-9477-4D9F64C2438F}">
-  <dimension ref="A1:G51"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.7265625" style="4" customWidth="1"/>
     <col min="2" max="2" width="21.6328125" style="4" customWidth="1"/>
     <col min="3" max="4" width="14.81640625" style="10" customWidth="1"/>
     <col min="5" max="5" width="19.6328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.6328125" style="4" customWidth="1"/>
-    <col min="7" max="7" width="37.36328125" style="4" customWidth="1"/>
-    <col min="8" max="16384" width="10.90625" style="4"/>
+    <col min="6" max="7" width="19.6328125" style="4" customWidth="1"/>
+    <col min="8" max="8" width="37.36328125" style="4" customWidth="1"/>
+    <col min="9" max="16384" width="10.90625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
       <c r="F1" s="3"/>
-    </row>
-    <row r="3" spans="1:7" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G1" s="3"/>
+    </row>
+    <row r="3" spans="1:9" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7" s="6" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" s="6" customFormat="1" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="8" t="s">
         <v>3</v>
       </c>
@@ -709,235 +715,265 @@
         <v>6</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="21"/>
-    </row>
-    <row r="5" spans="1:7" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I4" s="4"/>
+    </row>
+    <row r="5" spans="1:9" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="7"/>
       <c r="B5" s="7"/>
       <c r="C5" s="12"/>
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
-      <c r="F5" s="22"/>
-      <c r="G5" s="23"/>
-    </row>
-    <row r="6" spans="1:7" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+    </row>
+    <row r="6" spans="1:9" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="7"/>
       <c r="B6" s="7"/>
       <c r="C6" s="12"/>
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
-      <c r="F6" s="22"/>
-      <c r="G6" s="23"/>
-    </row>
-    <row r="7" spans="1:7" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+    </row>
+    <row r="7" spans="1:9" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="7"/>
       <c r="B7" s="7"/>
       <c r="C7" s="12"/>
       <c r="D7" s="7"/>
       <c r="E7" s="7"/>
-      <c r="F7" s="22"/>
-      <c r="G7" s="23"/>
-    </row>
-    <row r="8" spans="1:7" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+    </row>
+    <row r="8" spans="1:9" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="12"/>
       <c r="D8" s="7"/>
       <c r="E8" s="7"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="23"/>
-    </row>
-    <row r="9" spans="1:7" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+    </row>
+    <row r="9" spans="1:9" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="7"/>
       <c r="B9" s="7"/>
       <c r="C9" s="12"/>
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
-      <c r="F9" s="22"/>
-      <c r="G9" s="23"/>
-    </row>
-    <row r="10" spans="1:7" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+    </row>
+    <row r="10" spans="1:9" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
       <c r="C10" s="12"/>
       <c r="D10" s="7"/>
       <c r="E10" s="7"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="23"/>
-    </row>
-    <row r="11" spans="1:7" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+    </row>
+    <row r="11" spans="1:9" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
       <c r="C11" s="12"/>
       <c r="D11" s="7"/>
       <c r="E11" s="7"/>
-      <c r="F11" s="22"/>
-      <c r="G11" s="23"/>
-    </row>
-    <row r="12" spans="1:7" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+    </row>
+    <row r="12" spans="1:9" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="7"/>
       <c r="B12" s="7"/>
       <c r="C12" s="12"/>
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="23"/>
-    </row>
-    <row r="13" spans="1:7" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+    </row>
+    <row r="13" spans="1:9" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="7"/>
       <c r="B13" s="7"/>
       <c r="C13" s="12"/>
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="23"/>
-    </row>
-    <row r="14" spans="1:7" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+    </row>
+    <row r="14" spans="1:9" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="7"/>
       <c r="B14" s="7"/>
       <c r="C14" s="12"/>
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="23"/>
-    </row>
-    <row r="15" spans="1:7" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+    </row>
+    <row r="15" spans="1:9" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="7"/>
       <c r="B15" s="7"/>
       <c r="C15" s="12"/>
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="23"/>
-    </row>
-    <row r="16" spans="1:7" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+    </row>
+    <row r="16" spans="1:9" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="7"/>
       <c r="B16" s="7"/>
       <c r="C16" s="12"/>
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="23"/>
-    </row>
-    <row r="17" spans="1:7" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+    </row>
+    <row r="17" spans="1:8" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="7"/>
       <c r="B17" s="7"/>
       <c r="C17" s="12"/>
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="23"/>
-    </row>
-    <row r="18" spans="1:7" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+    </row>
+    <row r="18" spans="1:8" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="7"/>
       <c r="B18" s="7"/>
       <c r="C18" s="12"/>
       <c r="D18" s="7"/>
       <c r="E18" s="7"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="23"/>
-    </row>
-    <row r="19" spans="1:7" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+    </row>
+    <row r="19" spans="1:8" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="7"/>
       <c r="B19" s="7"/>
       <c r="C19" s="12"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
-      <c r="F19" s="22"/>
-      <c r="G19" s="23"/>
-    </row>
-    <row r="20" spans="1:7" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+    </row>
+    <row r="20" spans="1:8" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="12"/>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="23"/>
-    </row>
-    <row r="21" spans="1:7" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
+    </row>
+    <row r="21" spans="1:8" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="7"/>
       <c r="B21" s="7"/>
       <c r="C21" s="12"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
-      <c r="F21" s="22"/>
-      <c r="G21" s="23"/>
-    </row>
-    <row r="22" spans="1:7" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
+    </row>
+    <row r="22" spans="1:8" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="7"/>
       <c r="B22" s="7"/>
       <c r="C22" s="12"/>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="23"/>
-    </row>
-    <row r="23" spans="1:7" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
+    </row>
+    <row r="23" spans="1:8" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="7"/>
       <c r="B23" s="7"/>
       <c r="C23" s="12"/>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
-      <c r="F23" s="22"/>
-      <c r="G23" s="23"/>
-    </row>
-    <row r="24" spans="1:7" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
+    </row>
+    <row r="24" spans="1:8" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="7"/>
       <c r="B24" s="7"/>
       <c r="C24" s="12"/>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
-      <c r="F24" s="22"/>
-      <c r="G24" s="23"/>
-    </row>
-    <row r="25" spans="1:7" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+      <c r="H24" s="7"/>
+    </row>
+    <row r="25" spans="1:8" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="7"/>
       <c r="B25" s="7"/>
       <c r="C25" s="12"/>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
-      <c r="F25" s="22"/>
-      <c r="G25" s="23"/>
-    </row>
-    <row r="26" spans="1:7" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7"/>
+    </row>
+    <row r="26" spans="1:8" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="7"/>
       <c r="B26" s="7"/>
       <c r="C26" s="12"/>
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
-      <c r="F26" s="22"/>
-      <c r="G26" s="23"/>
-    </row>
-    <row r="27" spans="1:7" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
+      <c r="H26" s="7"/>
+    </row>
+    <row r="27" spans="1:8" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="7"/>
       <c r="B27" s="7"/>
       <c r="C27" s="12"/>
       <c r="D27" s="7"/>
       <c r="E27" s="7"/>
-      <c r="F27" s="22"/>
-      <c r="G27" s="23"/>
-    </row>
-    <row r="28" spans="1:7" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F27" s="7"/>
+      <c r="G27" s="7"/>
+      <c r="H27" s="7"/>
+    </row>
+    <row r="28" spans="1:8" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="7"/>
       <c r="B28" s="7"/>
       <c r="C28" s="12"/>
       <c r="D28" s="7"/>
       <c r="E28" s="7"/>
-      <c r="F28" s="22"/>
-      <c r="G28" s="23"/>
-    </row>
-    <row r="32" spans="1:7" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7"/>
+    </row>
+    <row r="32" spans="1:8" ht="20.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="1:7" s="5" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:8" s="5" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>2</v>
       </c>
@@ -951,171 +987,157 @@
         <v>9</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="G33" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G33" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="H33" s="22"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" s="7"/>
       <c r="B34" s="7"/>
       <c r="C34" s="12"/>
       <c r="D34" s="13"/>
       <c r="E34" s="7"/>
       <c r="F34" s="7"/>
-      <c r="G34" s="7"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G34" s="19"/>
+      <c r="H34" s="20"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" s="7"/>
       <c r="B35" s="7"/>
       <c r="C35" s="12"/>
       <c r="D35" s="13"/>
       <c r="E35" s="7"/>
       <c r="F35" s="7"/>
-      <c r="G35" s="7"/>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G35" s="19"/>
+      <c r="H35" s="20"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" s="7"/>
       <c r="B36" s="7"/>
       <c r="C36" s="12"/>
       <c r="D36" s="13"/>
       <c r="E36" s="7"/>
       <c r="F36" s="7"/>
-      <c r="G36" s="7"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G36" s="19"/>
+      <c r="H36" s="20"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37" s="7"/>
       <c r="B37" s="7"/>
       <c r="C37" s="12"/>
       <c r="D37" s="13"/>
       <c r="E37" s="7"/>
       <c r="F37" s="7"/>
-      <c r="G37" s="7"/>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G37" s="19"/>
+      <c r="H37" s="20"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38" s="7"/>
       <c r="B38" s="7"/>
       <c r="C38" s="12"/>
       <c r="D38" s="13"/>
       <c r="E38" s="7"/>
       <c r="F38" s="7"/>
-      <c r="G38" s="7"/>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G38" s="19"/>
+      <c r="H38" s="20"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" s="7"/>
       <c r="B39" s="7"/>
       <c r="C39" s="12"/>
       <c r="D39" s="13"/>
       <c r="E39" s="7"/>
       <c r="F39" s="7"/>
-      <c r="G39" s="7"/>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G39" s="19"/>
+      <c r="H39" s="20"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" s="7"/>
       <c r="B40" s="7"/>
       <c r="C40" s="12"/>
       <c r="D40" s="13"/>
       <c r="E40" s="7"/>
       <c r="F40" s="7"/>
-      <c r="G40" s="7"/>
-    </row>
-    <row r="42" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+      <c r="G40" s="19"/>
+      <c r="H40" s="20"/>
+    </row>
+    <row r="42" spans="1:8" ht="16" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C42" s="3"/>
       <c r="D42" s="3"/>
     </row>
-    <row r="44" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:8" ht="16" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="16" x14ac:dyDescent="0.35">
       <c r="A45" s="2"/>
     </row>
-    <row r="46" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="14"/>
       <c r="B46" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C46" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C46" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D46" s="18"/>
-    </row>
-    <row r="47" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D46" s="17"/>
+    </row>
+    <row r="47" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B47" s="14"/>
       <c r="C47" s="15"/>
-      <c r="D47" s="19"/>
-    </row>
-    <row r="48" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="48" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B48" s="14"/>
       <c r="C48" s="15"/>
-      <c r="D48" s="19"/>
-    </row>
-    <row r="49" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="49" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B49" s="16"/>
       <c r="C49" s="15"/>
-      <c r="D49" s="19"/>
-    </row>
-    <row r="50" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="50" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B50" s="14"/>
       <c r="C50" s="15"/>
-      <c r="D50" s="19"/>
-    </row>
-    <row r="51" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="51" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B51" s="14"/>
       <c r="C51" s="15"/>
-      <c r="D51" s="19"/>
     </row>
   </sheetData>
-  <mergeCells count="26">
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="F12:G12"/>
+  <mergeCells count="9">
     <mergeCell ref="B1:E1"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="G38:H38"/>
+    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="G37:H37"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5" xr:uid="{DDC592E5-6DE8-4F62-A67E-A4DCA977BC7D}">
@@ -1124,11 +1146,11 @@
     </dataValidation>
     <dataValidation errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Date" sqref="C6:D6" xr:uid="{B5EC2619-8B6C-4AE0-927F-DC3067E5D38B}"/>
   </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="67" orientation="landscape" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{896EA485-EDD9-4D6B-81F1-2056D0CBE04A}">
           <x14:formula1>
             <xm:f>Tabelle2!$A$1:$A$4</xm:f>
@@ -1141,6 +1163,12 @@
           </x14:formula1>
           <xm:sqref>F34:F40</xm:sqref>
         </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{3534D49D-8E8B-40F3-B132-F7C135FC85B2}">
+          <x14:formula1>
+            <xm:f>Tabelle2!$A$11:$A$13</xm:f>
+          </x14:formula1>
+          <xm:sqref>G5</xm:sqref>
+        </x14:dataValidation>
       </x14:dataValidations>
     </ext>
   </extLst>
@@ -1149,37 +1177,52 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48DB99CF-6F8C-44F8-A7A0-5E59BEE9A540}">
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
